--- a/InputData/indst/CRSW/Cement Overhaul Shareweight.xlsx
+++ b/InputData/indst/CRSW/Cement Overhaul Shareweight.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,6 +453,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -498,6 +499,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -550,6 +553,18 @@
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Written by Claude Code (Fable/Sonnet agent session), cement industry breakout, worktree cement-industry-breakout-f901fc, 2026-08-26. This is a DRAFT input for staff review, not a finished or approved EI position; verify all figures against primary sources before use in any work product. Reviewed by: (pending).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Recalibration 2026-10-01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CRSW re-solved to 0.1297 (all pathways) after the cement capital costs moved to the model's 2012 USD (greenfield 250, overhaul 25 $/(t/yr)) and the CCS pathway was reconciled with the CCS sector inputs. Two Newton passes with crsw_recal2.py on runs S7_Cal/S7_Cal2: facing-weighted mean dry-kiln overhaul share 0.2084 -&gt; 0.4857 (target 0.485). Note: the BAU now builds CCS kilns from 2030 because the 45Q-type subsidy (BCS) exceeds capture O&amp;M + T&amp;S + energy; team decision pending on whether BAU should include that.</t>
         </is>
       </c>
     </row>
@@ -577,6 +592,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -587,6 +603,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -618,6 +635,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1120,6 +1138,7 @@
         <v/>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
@@ -1149,7 +1168,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Unit: dimensionless (DRAFT 25 flat, steel SRSW draft value - calibrate to observed fleet longevity)</t>
+          <t>Unit: dimensionless by pathway (dry kiln RECALIBRATED 2026-10-01 after the 2012-USD capital-cost fix and CCS reconciliation: 0.1297 (was 0.03565) = facing-weighted mean dry-kiln overhaul share 0.485 over 2026-2050 in run S7_Cal2 = mean retirement age ~49 yr at CPPL 25 = US fleet mean operating age ~36 yr (PCA 2019); jointly identified with IELC -6 and the greenfield cost basis - re-solve whenever CPCC/CRCC/IELC change (crsw_recal2.py, 2 Newton passes); other pathways carry the same weight - judgment)</t>
         </is>
       </c>
       <c r="B1" t="n">
